--- a/Preliminary Data/two forces (40 trials)(optimized and cylindrical)/Validation(1.75).xlsx
+++ b/Preliminary Data/two forces (40 trials)(optimized and cylindrical)/Validation(1.75).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/two forces (40 trials)(optimized and cylindrical)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Bio-Inspired-Sensing/Preliminary Data/two forces (40 trials)(optimized and cylindrical)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2435" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43FB59DF-D7D7-4BAA-9146-4CE1AC6FAB4A}"/>
+  <xr:revisionPtr revIDLastSave="2440" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5F504B7-2D4C-4FCA-A755-119A6B4A00A4}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation (double)" sheetId="12" r:id="rId1"/>
@@ -909,29 +909,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B763EDC-8536-442D-A8D3-F37978D4DE80}">
   <dimension ref="A1:AC52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="33" t="s">
         <v>11</v>
       </c>
@@ -970,7 +971,7 @@
       <c r="AB1" s="40"/>
       <c r="AC1" s="41"/>
     </row>
-    <row r="2" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -1059,7 +1060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>0.2</v>
       </c>
@@ -1132,16 +1133,16 @@
         <v>0.1988</v>
       </c>
       <c r="X3" s="8">
-        <f t="shared" ref="X3:AC3" si="0">ABS(L3-R3)</f>
-        <v>7.8469540625810622E-4</v>
+        <f>L3-R3</f>
+        <v>-7.8469540625810622E-4</v>
       </c>
       <c r="Y3" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="Y3:AC3" si="0">M3-S3</f>
         <v>2.6451368005573704E-2</v>
       </c>
       <c r="Z3" s="8">
         <f t="shared" si="0"/>
-        <v>7.8847019672398377E-4</v>
+        <v>-7.8847019672398377E-4</v>
       </c>
       <c r="AA3" s="8">
         <f t="shared" si="0"/>
@@ -1153,10 +1154,10 @@
       </c>
       <c r="AC3" s="8">
         <f t="shared" si="0"/>
-        <v>0.16959497575759891</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>-0.16959497575759891</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>1</v>
       </c>
@@ -1229,31 +1230,31 @@
         <v>0.95799999999999996</v>
       </c>
       <c r="X4" s="8">
-        <f t="shared" ref="X4:X42" si="3">ABS(L4-R4)</f>
-        <v>1.30488071590662E-3</v>
+        <f t="shared" ref="X4:X42" si="3">L4-R4</f>
+        <v>-1.30488071590662E-3</v>
       </c>
       <c r="Y4" s="8">
-        <f t="shared" ref="Y4:Y42" si="4">ABS(M4-S4)</f>
-        <v>1.9995363712309866E-3</v>
+        <f t="shared" ref="Y4:Y42" si="4">M4-S4</f>
+        <v>-1.9995363712309866E-3</v>
       </c>
       <c r="Z4" s="8">
-        <f t="shared" ref="Z4:Z42" si="5">ABS(N4-T4)</f>
+        <f t="shared" ref="Z4:Z42" si="5">N4-T4</f>
         <v>1.8193194699286985E-2</v>
       </c>
       <c r="AA4" s="8">
-        <f t="shared" ref="AA4:AA42" si="6">ABS(O4-U4)</f>
-        <v>8.2416601133346978E-2</v>
+        <f t="shared" ref="AA4:AA42" si="6">O4-U4</f>
+        <v>-8.2416601133346978E-2</v>
       </c>
       <c r="AB4" s="8">
-        <f t="shared" ref="AB4:AB42" si="7">ABS(P4-V4)</f>
+        <f t="shared" ref="AB4:AB42" si="7">P4-V4</f>
         <v>0.15957424840927104</v>
       </c>
       <c r="AC4" s="8">
-        <f t="shared" ref="AC4:AC42" si="8">ABS(Q4-W4)</f>
-        <v>3.3168251991271935E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+        <f t="shared" ref="AC4:AC42" si="8">Q4-W4</f>
+        <v>-3.3168251991271935E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>0.5</v>
       </c>
@@ -1327,11 +1328,11 @@
       </c>
       <c r="X5" s="8">
         <f t="shared" si="3"/>
-        <v>8.8173459516838206E-5</v>
+        <v>-8.8173459516838206E-5</v>
       </c>
       <c r="Y5" s="8">
         <f t="shared" si="4"/>
-        <v>1.1049709784984596E-2</v>
+        <v>-1.1049709784984596E-2</v>
       </c>
       <c r="Z5" s="8">
         <f t="shared" si="5"/>
@@ -1339,18 +1340,18 @@
       </c>
       <c r="AA5" s="8">
         <f t="shared" si="6"/>
-        <v>6.9445213019848004E-3</v>
+        <v>-6.9445213019848004E-3</v>
       </c>
       <c r="AB5" s="8">
         <f t="shared" si="7"/>
-        <v>1.0517201423650147E-3</v>
+        <v>-1.0517201423650147E-3</v>
       </c>
       <c r="AC5" s="8">
         <f t="shared" si="8"/>
         <v>4.8466738080978011E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>0.9</v>
       </c>
@@ -1428,7 +1429,7 @@
       </c>
       <c r="Y6" s="8">
         <f t="shared" si="4"/>
-        <v>1.9794370245934001E-2</v>
+        <v>-1.9794370245934001E-2</v>
       </c>
       <c r="Z6" s="8">
         <f t="shared" si="5"/>
@@ -1436,7 +1437,7 @@
       </c>
       <c r="AA6" s="8">
         <f t="shared" si="6"/>
-        <v>8.559644753932999E-2</v>
+        <v>-8.559644753932999E-2</v>
       </c>
       <c r="AB6" s="8">
         <f t="shared" si="7"/>
@@ -1447,7 +1448,7 @@
         <v>7.3164005184173986E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>0.1</v>
       </c>
@@ -1521,15 +1522,15 @@
       </c>
       <c r="X7" s="8">
         <f t="shared" si="3"/>
-        <v>3.3720862120389898E-5</v>
+        <v>-3.3720862120389898E-5</v>
       </c>
       <c r="Y7" s="8">
         <f t="shared" si="4"/>
-        <v>2.9111583584547004E-2</v>
+        <v>-2.9111583584547004E-2</v>
       </c>
       <c r="Z7" s="8">
         <f t="shared" si="5"/>
-        <v>1.0434491753579939E-3</v>
+        <v>-1.0434491753579939E-3</v>
       </c>
       <c r="AA7" s="8">
         <f t="shared" si="6"/>
@@ -1544,7 +1545,7 @@
         <v>0.16765497174263</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>0.8</v>
       </c>
@@ -1630,7 +1631,7 @@
       </c>
       <c r="AA8" s="8">
         <f t="shared" si="6"/>
-        <v>6.9419154500961033E-2</v>
+        <v>-6.9419154500961033E-2</v>
       </c>
       <c r="AB8" s="8">
         <f t="shared" si="7"/>
@@ -1638,10 +1639,10 @@
       </c>
       <c r="AC8" s="8">
         <f t="shared" si="8"/>
-        <v>5.6910971570014998E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-5.6910971570014998E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>0.1</v>
       </c>
@@ -1715,7 +1716,7 @@
       </c>
       <c r="X9" s="8">
         <f t="shared" si="3"/>
-        <v>3.4698794540017795E-4</v>
+        <v>-3.4698794540017795E-4</v>
       </c>
       <c r="Y9" s="8">
         <f t="shared" si="4"/>
@@ -1723,7 +1724,7 @@
       </c>
       <c r="Z9" s="8">
         <f t="shared" si="5"/>
-        <v>1.2968880459665998E-3</v>
+        <v>-1.2968880459665998E-3</v>
       </c>
       <c r="AA9" s="8">
         <f t="shared" si="6"/>
@@ -1731,14 +1732,14 @@
       </c>
       <c r="AB9" s="8">
         <f t="shared" si="7"/>
-        <v>8.3639538407330044E-3</v>
+        <v>-8.3639538407330044E-3</v>
       </c>
       <c r="AC9" s="8">
         <f t="shared" si="8"/>
-        <v>8.1221710073947906E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-8.1221710073947906E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>0.9</v>
       </c>
@@ -1812,7 +1813,7 @@
       </c>
       <c r="X10" s="8">
         <f t="shared" si="3"/>
-        <v>8.9414953254163298E-4</v>
+        <v>-8.9414953254163298E-4</v>
       </c>
       <c r="Y10" s="8">
         <f t="shared" si="4"/>
@@ -1832,10 +1833,10 @@
       </c>
       <c r="AC10" s="8">
         <f t="shared" si="8"/>
-        <v>0.10243778638839696</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-0.10243778638839696</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>0.3</v>
       </c>
@@ -1909,7 +1910,7 @@
       </c>
       <c r="X11" s="8">
         <f t="shared" si="3"/>
-        <v>3.5819396786391697E-4</v>
+        <v>-3.5819396786391697E-4</v>
       </c>
       <c r="Y11" s="8">
         <f t="shared" si="4"/>
@@ -1917,7 +1918,7 @@
       </c>
       <c r="Z11" s="8">
         <f t="shared" si="5"/>
-        <v>4.1187301442027098E-3</v>
+        <v>-4.1187301442027098E-3</v>
       </c>
       <c r="AA11" s="8">
         <f t="shared" si="6"/>
@@ -1925,14 +1926,14 @@
       </c>
       <c r="AB11" s="8">
         <f t="shared" si="7"/>
-        <v>2.0599879658222197E-2</v>
+        <v>-2.0599879658222197E-2</v>
       </c>
       <c r="AC11" s="8">
         <f t="shared" si="8"/>
         <v>2.1234368610381971E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>0.9</v>
       </c>
@@ -2006,7 +2007,7 @@
       </c>
       <c r="X12" s="8">
         <f t="shared" si="3"/>
-        <v>2.3589301973581311E-3</v>
+        <v>-2.3589301973581311E-3</v>
       </c>
       <c r="Y12" s="8">
         <f t="shared" si="4"/>
@@ -2026,10 +2027,10 @@
       </c>
       <c r="AC12" s="8">
         <f t="shared" si="8"/>
-        <v>0.33929155693054203</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-0.33929155693054203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>0.1</v>
       </c>
@@ -2103,7 +2104,7 @@
       </c>
       <c r="X13" s="8">
         <f t="shared" si="3"/>
-        <v>3.41577096655965E-4</v>
+        <v>-3.41577096655965E-4</v>
       </c>
       <c r="Y13" s="8">
         <f t="shared" si="4"/>
@@ -2123,10 +2124,10 @@
       </c>
       <c r="AC13" s="8">
         <f t="shared" si="8"/>
-        <v>0.1354084673881531</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-0.1354084673881531</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>0.9</v>
       </c>
@@ -2208,7 +2209,7 @@
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="5"/>
-        <v>8.1324358031153697E-3</v>
+        <v>-8.1324358031153697E-3</v>
       </c>
       <c r="AA14" s="8">
         <f t="shared" si="6"/>
@@ -2216,14 +2217,14 @@
       </c>
       <c r="AB14" s="8">
         <f t="shared" si="7"/>
-        <v>2.5331639635562897E-2</v>
+        <v>-2.5331639635562897E-2</v>
       </c>
       <c r="AC14" s="8">
         <f t="shared" si="8"/>
-        <v>0.2541238607168198</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-0.2541238607168198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>0.9</v>
       </c>
@@ -2297,30 +2298,30 @@
       </c>
       <c r="X15" s="8">
         <f t="shared" si="3"/>
-        <v>1.5117256850004199E-3</v>
+        <v>-1.5117256850004199E-3</v>
       </c>
       <c r="Y15" s="8">
         <f t="shared" si="4"/>
-        <v>1.8113092827796901E-2</v>
+        <v>-1.8113092827796901E-2</v>
       </c>
       <c r="Z15" s="8">
         <f t="shared" si="5"/>
-        <v>1.1289192223549002E-2</v>
+        <v>-1.1289192223549002E-2</v>
       </c>
       <c r="AA15" s="8">
         <f t="shared" si="6"/>
-        <v>0.12012213902473501</v>
+        <v>-0.12012213902473501</v>
       </c>
       <c r="AB15" s="8">
         <f t="shared" si="7"/>
-        <v>1.3265609741209827E-3</v>
+        <v>-1.3265609741209827E-3</v>
       </c>
       <c r="AC15" s="8">
         <f t="shared" si="8"/>
         <v>9.0605189990997009E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>0.4</v>
       </c>
@@ -2394,7 +2395,7 @@
       </c>
       <c r="X16" s="8">
         <f t="shared" si="3"/>
-        <v>4.0076037213206302E-3</v>
+        <v>-4.0076037213206302E-3</v>
       </c>
       <c r="Y16" s="8">
         <f t="shared" si="4"/>
@@ -2414,10 +2415,10 @@
       </c>
       <c r="AC16" s="8">
         <f t="shared" si="8"/>
-        <v>3.2842726016044987E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-3.2842726016044987E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A17" s="10">
         <v>1</v>
       </c>
@@ -2491,30 +2492,30 @@
       </c>
       <c r="X17" s="8">
         <f t="shared" si="3"/>
-        <v>5.8661292344331989E-4</v>
+        <v>-5.8661292344331989E-4</v>
       </c>
       <c r="Y17" s="8">
         <f t="shared" si="4"/>
-        <v>1.7105522179603996E-2</v>
+        <v>-1.7105522179603996E-2</v>
       </c>
       <c r="Z17" s="8">
         <f t="shared" si="5"/>
-        <v>1.3202454876899999E-2</v>
+        <v>-1.3202454876899999E-2</v>
       </c>
       <c r="AA17" s="8">
         <f t="shared" si="6"/>
-        <v>2.9259641408920012E-2</v>
+        <v>-2.9259641408920012E-2</v>
       </c>
       <c r="AB17" s="8">
         <f t="shared" si="7"/>
-        <v>1.7651620674132951E-2</v>
+        <v>-1.7651620674132951E-2</v>
       </c>
       <c r="AC17" s="8">
         <f t="shared" si="8"/>
         <v>6.5874221420287982E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
         <v>0.4</v>
       </c>
@@ -2608,10 +2609,10 @@
       </c>
       <c r="AC18" s="8">
         <f t="shared" si="8"/>
-        <v>2.7495318603516006E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-2.7495318603516006E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>0.1</v>
       </c>
@@ -2685,7 +2686,7 @@
       </c>
       <c r="X19" s="8">
         <f t="shared" si="3"/>
-        <v>9.4886210495606096E-4</v>
+        <v>-9.4886210495606096E-4</v>
       </c>
       <c r="Y19" s="8">
         <f t="shared" si="4"/>
@@ -2705,10 +2706,10 @@
       </c>
       <c r="AC19" s="8">
         <f t="shared" si="8"/>
-        <v>2.8661772584915007E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-2.8661772584915007E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>0.9</v>
       </c>
@@ -2782,7 +2783,7 @@
       </c>
       <c r="X20" s="8">
         <f t="shared" si="3"/>
-        <v>4.3503133229911301E-3</v>
+        <v>-4.3503133229911301E-3</v>
       </c>
       <c r="Y20" s="8">
         <f t="shared" si="4"/>
@@ -2802,10 +2803,10 @@
       </c>
       <c r="AC20" s="8">
         <f t="shared" si="8"/>
-        <v>0.15892959547042801</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-0.15892959547042801</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>0.1</v>
       </c>
@@ -2902,7 +2903,7 @@
         <v>6.7859151124950168E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>0.1</v>
       </c>
@@ -2999,7 +3000,7 @@
         <v>2.3799663257598969E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <v>0.9</v>
       </c>
@@ -3073,7 +3074,7 @@
       </c>
       <c r="X23" s="8">
         <f t="shared" si="3"/>
-        <v>1.4453361794352503E-3</v>
+        <v>-1.4453361794352503E-3</v>
       </c>
       <c r="Y23" s="8">
         <f t="shared" si="4"/>
@@ -3081,7 +3082,7 @@
       </c>
       <c r="Z23" s="8">
         <f t="shared" si="5"/>
-        <v>3.830093121528988E-3</v>
+        <v>-3.830093121528988E-3</v>
       </c>
       <c r="AA23" s="8">
         <f t="shared" si="6"/>
@@ -3093,10 +3094,10 @@
       </c>
       <c r="AC23" s="8">
         <f t="shared" si="8"/>
-        <v>7.7740104007720912E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-7.7740104007720912E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>0.2</v>
       </c>
@@ -3170,11 +3171,11 @@
       </c>
       <c r="X24" s="8">
         <f t="shared" si="3"/>
-        <v>7.4009120948612703E-4</v>
+        <v>-7.4009120948612703E-4</v>
       </c>
       <c r="Y24" s="8">
         <f t="shared" si="4"/>
-        <v>4.7156942248344005E-3</v>
+        <v>-4.7156942248344005E-3</v>
       </c>
       <c r="Z24" s="8">
         <f t="shared" si="5"/>
@@ -3193,7 +3194,7 @@
         <v>4.3655904674529955E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>0.6</v>
       </c>
@@ -3287,10 +3288,10 @@
       </c>
       <c r="AC25" s="8">
         <f t="shared" si="8"/>
-        <v>3.7380270195007004E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-3.7380270195007004E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>0.7</v>
       </c>
@@ -3364,15 +3365,15 @@
       </c>
       <c r="X26" s="8">
         <f t="shared" si="3"/>
-        <v>1.8902514070272397E-3</v>
+        <v>-1.8902514070272397E-3</v>
       </c>
       <c r="Y26" s="8">
         <f t="shared" si="4"/>
-        <v>9.4167374610900079E-3</v>
+        <v>-9.4167374610900079E-3</v>
       </c>
       <c r="Z26" s="8">
         <f t="shared" si="5"/>
-        <v>4.228285646438984E-3</v>
+        <v>-4.228285646438984E-3</v>
       </c>
       <c r="AA26" s="8">
         <f t="shared" si="6"/>
@@ -3380,14 +3381,14 @@
       </c>
       <c r="AB26" s="8">
         <f t="shared" si="7"/>
-        <v>4.4208440780640013E-2</v>
+        <v>-4.4208440780640013E-2</v>
       </c>
       <c r="AC26" s="8">
         <f t="shared" si="8"/>
         <v>0.10656875114441</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>0.1</v>
       </c>
@@ -3461,7 +3462,7 @@
       </c>
       <c r="X27" s="8">
         <f t="shared" si="3"/>
-        <v>2.2198281854391099E-3</v>
+        <v>-2.2198281854391099E-3</v>
       </c>
       <c r="Y27" s="8">
         <f t="shared" si="4"/>
@@ -3469,22 +3470,22 @@
       </c>
       <c r="Z27" s="8">
         <f t="shared" si="5"/>
-        <v>9.159550499915986E-3</v>
+        <v>-9.159550499915986E-3</v>
       </c>
       <c r="AA27" s="8">
         <f t="shared" si="6"/>
-        <v>7.5163779258699548E-4</v>
+        <v>-7.5163779258699548E-4</v>
       </c>
       <c r="AB27" s="8">
         <f t="shared" si="7"/>
-        <v>1.2716566181182998E-2</v>
+        <v>-1.2716566181182998E-2</v>
       </c>
       <c r="AC27" s="8">
         <f t="shared" si="8"/>
         <v>2.2900347042083699E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>1</v>
       </c>
@@ -3558,7 +3559,7 @@
       </c>
       <c r="X28" s="8">
         <f t="shared" si="3"/>
-        <v>9.0747634395956997E-4</v>
+        <v>-9.0747634395956997E-4</v>
       </c>
       <c r="Y28" s="8">
         <f t="shared" si="4"/>
@@ -3566,7 +3567,7 @@
       </c>
       <c r="Z28" s="8">
         <f t="shared" si="5"/>
-        <v>1.1353018355370004E-2</v>
+        <v>-1.1353018355370004E-2</v>
       </c>
       <c r="AA28" s="8">
         <f t="shared" si="6"/>
@@ -3574,14 +3575,14 @@
       </c>
       <c r="AB28" s="8">
         <f t="shared" si="7"/>
-        <v>8.1717041110991984E-2</v>
+        <v>-8.1717041110991984E-2</v>
       </c>
       <c r="AC28" s="8">
         <f t="shared" si="8"/>
-        <v>9.8051102924347044E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-9.8051102924347044E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <v>0.7</v>
       </c>
@@ -3655,11 +3656,11 @@
       </c>
       <c r="X29" s="8">
         <f t="shared" si="3"/>
-        <v>2.4698124080896398E-4</v>
+        <v>-2.4698124080896398E-4</v>
       </c>
       <c r="Y29" s="8">
         <f t="shared" si="4"/>
-        <v>3.5693909072876007E-2</v>
+        <v>-3.5693909072876007E-2</v>
       </c>
       <c r="Z29" s="8">
         <f t="shared" si="5"/>
@@ -3678,7 +3679,7 @@
         <v>0.23825191392898598</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
         <v>1</v>
       </c>
@@ -3752,11 +3753,11 @@
       </c>
       <c r="X30" s="8">
         <f t="shared" si="3"/>
-        <v>3.5340974763035798E-3</v>
+        <v>-3.5340974763035798E-3</v>
       </c>
       <c r="Y30" s="8">
         <f t="shared" si="4"/>
-        <v>4.5105752944901711E-4</v>
+        <v>-4.5105752944901711E-4</v>
       </c>
       <c r="Z30" s="8">
         <f t="shared" si="5"/>
@@ -3775,7 +3776,7 @@
         <v>4.9476130867003976E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
         <v>0.1</v>
       </c>
@@ -3849,30 +3850,30 @@
       </c>
       <c r="X31" s="8">
         <f t="shared" si="3"/>
-        <v>2.4949701037257899E-4</v>
+        <v>-2.4949701037257899E-4</v>
       </c>
       <c r="Y31" s="8">
         <f t="shared" si="4"/>
-        <v>7.8116000220179987E-3</v>
+        <v>-7.8116000220179987E-3</v>
       </c>
       <c r="Z31" s="8">
         <f t="shared" si="5"/>
-        <v>1.4442876487970012E-3</v>
+        <v>-1.4442876487970012E-3</v>
       </c>
       <c r="AA31" s="8">
         <f t="shared" si="6"/>
-        <v>1.9918696559965603E-3</v>
+        <v>-1.9918696559965603E-3</v>
       </c>
       <c r="AB31" s="8">
         <f t="shared" si="7"/>
-        <v>4.8862874507899778E-3</v>
+        <v>-4.8862874507899778E-3</v>
       </c>
       <c r="AC31" s="8">
         <f t="shared" si="8"/>
         <v>3.1922299957275399E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
         <v>0.3</v>
       </c>
@@ -3950,7 +3951,7 @@
       </c>
       <c r="Y32" s="8">
         <f t="shared" si="4"/>
-        <v>7.3446123719220074E-3</v>
+        <v>-7.3446123719220074E-3</v>
       </c>
       <c r="Z32" s="8">
         <f t="shared" si="5"/>
@@ -3958,7 +3959,7 @@
       </c>
       <c r="AA32" s="8">
         <f t="shared" si="6"/>
-        <v>6.1520835518836942E-3</v>
+        <v>-6.1520835518836942E-3</v>
       </c>
       <c r="AB32" s="8">
         <f t="shared" si="7"/>
@@ -3969,7 +3970,7 @@
         <v>6.7981694507598944E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>1</v>
       </c>
@@ -4051,22 +4052,22 @@
       </c>
       <c r="Z33" s="8">
         <f t="shared" si="5"/>
-        <v>3.2264472149312502E-3</v>
+        <v>-3.2264472149312502E-3</v>
       </c>
       <c r="AA33" s="8">
         <f t="shared" si="6"/>
-        <v>9.2047486782070309E-3</v>
+        <v>-9.2047486782070309E-3</v>
       </c>
       <c r="AB33" s="8">
         <f t="shared" si="7"/>
-        <v>2.6735983109474198E-2</v>
+        <v>-2.6735983109474198E-2</v>
       </c>
       <c r="AC33" s="8">
         <f t="shared" si="8"/>
-        <v>0.10296625537872006</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-0.10296625537872006</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <v>0.1</v>
       </c>
@@ -4140,15 +4141,15 @@
       </c>
       <c r="X34" s="8">
         <f t="shared" si="3"/>
-        <v>1.2623867012560399E-3</v>
+        <v>-1.2623867012560399E-3</v>
       </c>
       <c r="Y34" s="8">
         <f t="shared" si="4"/>
-        <v>2.0254774188994989E-2</v>
+        <v>-2.0254774188994989E-2</v>
       </c>
       <c r="Z34" s="8">
         <f t="shared" si="5"/>
-        <v>2.44302263647318E-2</v>
+        <v>-2.44302263647318E-2</v>
       </c>
       <c r="AA34" s="8">
         <f t="shared" si="6"/>
@@ -4156,14 +4157,14 @@
       </c>
       <c r="AB34" s="8">
         <f t="shared" si="7"/>
-        <v>0.14630638976097102</v>
+        <v>-0.14630638976097102</v>
       </c>
       <c r="AC34" s="8">
         <f t="shared" si="8"/>
         <v>0.1380458810806271</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A35" s="10">
         <v>0.9</v>
       </c>
@@ -4237,7 +4238,7 @@
       </c>
       <c r="X35" s="8">
         <f t="shared" si="3"/>
-        <v>7.8027322888374296E-4</v>
+        <v>-7.8027322888374296E-4</v>
       </c>
       <c r="Y35" s="8">
         <f t="shared" si="4"/>
@@ -4249,7 +4250,7 @@
       </c>
       <c r="AA35" s="8">
         <f t="shared" si="6"/>
-        <v>6.2587542152405029E-2</v>
+        <v>-6.2587542152405029E-2</v>
       </c>
       <c r="AB35" s="8">
         <f t="shared" si="7"/>
@@ -4257,10 +4258,10 @@
       </c>
       <c r="AC35" s="8">
         <f t="shared" si="8"/>
-        <v>0.11580813989639305</v>
-      </c>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-0.11580813989639305</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <v>1</v>
       </c>
@@ -4334,7 +4335,7 @@
       </c>
       <c r="X36" s="8">
         <f t="shared" si="3"/>
-        <v>3.1540230728685898E-3</v>
+        <v>-3.1540230728685898E-3</v>
       </c>
       <c r="Y36" s="8">
         <f t="shared" si="4"/>
@@ -4346,7 +4347,7 @@
       </c>
       <c r="AA36" s="8">
         <f t="shared" si="6"/>
-        <v>0.15963183479309107</v>
+        <v>-0.15963183479309107</v>
       </c>
       <c r="AB36" s="8">
         <f t="shared" si="7"/>
@@ -4354,10 +4355,10 @@
       </c>
       <c r="AC36" s="8">
         <f t="shared" si="8"/>
-        <v>8.0808059692379919E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
+        <v>-8.0808059692379919E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>0.3</v>
       </c>
@@ -4435,11 +4436,11 @@
       </c>
       <c r="Y37" s="8">
         <f t="shared" si="4"/>
-        <v>2.0519788390398003E-2</v>
+        <v>-2.0519788390398003E-2</v>
       </c>
       <c r="Z37" s="8">
         <f t="shared" si="5"/>
-        <v>4.9395880520343993E-3</v>
+        <v>-4.9395880520343993E-3</v>
       </c>
       <c r="AA37" s="8">
         <f t="shared" si="6"/>
@@ -4447,14 +4448,14 @@
       </c>
       <c r="AB37" s="8">
         <f t="shared" si="7"/>
-        <v>2.1886486625670998E-2</v>
+        <v>-2.1886486625670998E-2</v>
       </c>
       <c r="AC37" s="8">
         <f t="shared" si="8"/>
         <v>7.3134875679015998E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>0.9</v>
       </c>
@@ -4532,11 +4533,11 @@
       </c>
       <c r="Y38" s="8">
         <f t="shared" si="4"/>
-        <v>9.6941226243970058E-3</v>
+        <v>-9.6941226243970058E-3</v>
       </c>
       <c r="Z38" s="8">
         <f t="shared" si="5"/>
-        <v>6.3023253858089032E-3</v>
+        <v>-6.3023253858089032E-3</v>
       </c>
       <c r="AA38" s="8">
         <f t="shared" si="6"/>
@@ -4544,14 +4545,14 @@
       </c>
       <c r="AB38" s="8">
         <f t="shared" si="7"/>
-        <v>3.8712141513823989E-2</v>
+        <v>-3.8712141513823989E-2</v>
       </c>
       <c r="AC38" s="8">
         <f t="shared" si="8"/>
         <v>6.6518873405457035E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>0.1</v>
       </c>
@@ -4629,7 +4630,7 @@
       </c>
       <c r="Y39" s="8">
         <f t="shared" si="4"/>
-        <v>1.8872112774848987E-2</v>
+        <v>-1.8872112774848987E-2</v>
       </c>
       <c r="Z39" s="8">
         <f t="shared" si="5"/>
@@ -4637,7 +4638,7 @@
       </c>
       <c r="AA39" s="8">
         <f t="shared" si="6"/>
-        <v>6.8021567344666023E-3</v>
+        <v>-6.8021567344666023E-3</v>
       </c>
       <c r="AB39" s="8">
         <f t="shared" si="7"/>
@@ -4648,7 +4649,7 @@
         <v>0.10128984146118192</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
         <v>0.8</v>
       </c>
@@ -4722,15 +4723,15 @@
       </c>
       <c r="X40" s="8">
         <f t="shared" si="3"/>
-        <v>7.6683777570724001E-4</v>
+        <v>-7.6683777570724001E-4</v>
       </c>
       <c r="Y40" s="8">
         <f t="shared" si="4"/>
-        <v>6.6033444404599573E-3</v>
+        <v>-6.6033444404599573E-3</v>
       </c>
       <c r="Z40" s="8">
         <f t="shared" si="5"/>
-        <v>1.59464346408844E-2</v>
+        <v>-1.59464346408844E-2</v>
       </c>
       <c r="AA40" s="8">
         <f t="shared" si="6"/>
@@ -4738,14 +4739,14 @@
       </c>
       <c r="AB40" s="8">
         <f t="shared" si="7"/>
-        <v>9.7060062265395985E-2</v>
+        <v>-9.7060062265395985E-2</v>
       </c>
       <c r="AC40" s="8">
         <f t="shared" si="8"/>
         <v>2.1069674110409942E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A41" s="10">
         <v>1</v>
       </c>
@@ -4819,15 +4820,15 @@
       </c>
       <c r="X41" s="8">
         <f t="shared" si="3"/>
-        <v>3.8707862898707014E-3</v>
+        <v>-3.8707862898707014E-3</v>
       </c>
       <c r="Y41" s="8">
         <f t="shared" si="4"/>
-        <v>4.1152343511580147E-3</v>
+        <v>-4.1152343511580147E-3</v>
       </c>
       <c r="Z41" s="8">
         <f t="shared" si="5"/>
-        <v>7.2803380846976906E-3</v>
+        <v>-7.2803380846976906E-3</v>
       </c>
       <c r="AA41" s="8">
         <f t="shared" si="6"/>
@@ -4842,7 +4843,7 @@
         <v>3.0928960800169492E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A42" s="10">
         <v>0.2</v>
       </c>
@@ -4920,11 +4921,11 @@
       </c>
       <c r="Y42" s="8">
         <f t="shared" si="4"/>
-        <v>1.4705369114875806E-2</v>
+        <v>-1.4705369114875806E-2</v>
       </c>
       <c r="Z42" s="8">
         <f t="shared" si="5"/>
-        <v>2.3192345276475002E-3</v>
+        <v>-2.3192345276475002E-3</v>
       </c>
       <c r="AA42" s="8">
         <f t="shared" si="6"/>
@@ -4932,14 +4933,14 @@
       </c>
       <c r="AB42" s="8">
         <f t="shared" si="7"/>
-        <v>1.5283420300483699E-2</v>
+        <v>-1.5283420300483699E-2</v>
       </c>
       <c r="AC42" s="8">
         <f t="shared" si="8"/>
         <v>5.8561345481873028E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="8"/>
@@ -4970,7 +4971,7 @@
       <c r="AB43" s="7"/>
       <c r="AC43" s="7"/>
     </row>
-    <row r="44" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="8"/>
@@ -4996,30 +4997,30 @@
       <c r="W44" s="8"/>
       <c r="X44" s="7">
         <f>AVERAGE(X3:X42)</f>
-        <v>1.3409449074219437E-3</v>
+        <v>-6.0826974571566005E-4</v>
       </c>
       <c r="Y44" s="7">
         <f t="shared" ref="Y44:AC44" si="9">AVERAGE(Y3:Y42)</f>
-        <v>1.7838622469175589E-2</v>
+        <v>4.970013891104603E-3</v>
       </c>
       <c r="Z44" s="7">
         <f t="shared" si="9"/>
-        <v>8.1971452639624832E-3</v>
+        <v>1.480572763532357E-3</v>
       </c>
       <c r="AA44" s="7">
         <f t="shared" si="9"/>
-        <v>6.5999680939633459E-2</v>
+        <v>3.3955662026237718E-2</v>
       </c>
       <c r="AB44" s="7">
         <f t="shared" si="9"/>
-        <v>4.2622724233418681E-2</v>
+        <v>1.4430814532190575E-2</v>
       </c>
       <c r="AC44" s="7">
         <f t="shared" si="9"/>
-        <v>8.6322410710155756E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+        <v>-1.0319635569155121E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" s="8"/>
@@ -5050,7 +5051,7 @@
       <c r="AB45" s="7"/>
       <c r="AC45" s="7"/>
     </row>
-    <row r="46" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="8"/>
@@ -5099,7 +5100,7 @@
         <v>0.11121743282969934</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" s="8"/>
@@ -5130,7 +5131,7 @@
       <c r="AB47" s="7"/>
       <c r="AC47" s="7"/>
     </row>
-    <row r="48" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="8"/>
@@ -5161,7 +5162,7 @@
       <c r="AB48" s="7"/>
       <c r="AC48" s="7"/>
     </row>
-    <row r="49" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A49" s="8"/>
       <c r="B49" s="9"/>
       <c r="C49" s="8"/>
@@ -5192,7 +5193,7 @@
       <c r="AB49" s="7"/>
       <c r="AC49" s="7"/>
     </row>
-    <row r="50" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="8"/>
@@ -5223,7 +5224,7 @@
       <c r="AB50" s="7"/>
       <c r="AC50" s="7"/>
     </row>
-    <row r="51" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A51" s="8"/>
       <c r="B51" s="9"/>
       <c r="C51" s="8"/>
@@ -5254,7 +5255,7 @@
       <c r="AB51" s="7"/>
       <c r="AC51" s="7"/>
     </row>
-    <row r="52" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="16" x14ac:dyDescent="0.4">
       <c r="A52" s="8"/>
       <c r="B52" s="9"/>
       <c r="C52" s="8"/>
@@ -5300,41 +5301,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309BE333-3BAE-4E8D-AF02-67A9E2013036}">
   <dimension ref="A1:AU52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7265625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.140625" customWidth="1"/>
-    <col min="36" max="36" width="15.28515625" customWidth="1"/>
-    <col min="37" max="39" width="16.28515625" customWidth="1"/>
+    <col min="28" max="28" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.1796875" customWidth="1"/>
+    <col min="36" max="36" width="15.26953125" customWidth="1"/>
+    <col min="37" max="39" width="16.26953125" customWidth="1"/>
     <col min="40" max="40" width="11" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:47" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="33" t="s">
         <v>11</v>
       </c>
@@ -5393,7 +5394,7 @@
       <c r="AT1" s="44"/>
       <c r="AU1" s="44"/>
     </row>
-    <row r="2" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -5520,7 +5521,7 @@
       <c r="AT2" s="42"/>
       <c r="AU2" s="42"/>
     </row>
-    <row r="3" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:47" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="10">
         <f>'Proximal Validation (double)'!A3</f>
         <v>0.2</v>
@@ -5690,7 +5691,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:47" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <f>'Proximal Validation (double)'!A4</f>
         <v>1</v>
@@ -5868,7 +5869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <f>'Proximal Validation (double)'!A5</f>
         <v>0.5</v>
@@ -6024,7 +6025,7 @@
       <c r="AT5" s="42"/>
       <c r="AU5" s="42"/>
     </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <f>'Proximal Validation (double)'!A6</f>
         <v>0.9</v>
@@ -6184,7 +6185,7 @@
       <c r="AT6" s="21"/>
       <c r="AU6" s="21"/>
     </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <f>'Proximal Validation (double)'!A7</f>
         <v>0.1</v>
@@ -6347,7 +6348,7 @@
       <c r="AT7" s="21"/>
       <c r="AU7" s="21"/>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <f>'Proximal Validation (double)'!A8</f>
         <v>0.8</v>
@@ -6496,7 +6497,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <f>'Proximal Validation (double)'!A9</f>
         <v>0.1</v>
@@ -6654,7 +6655,7 @@
         <v>0.5614664099551141</v>
       </c>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <f>'Proximal Validation (double)'!A10</f>
         <v>0.9</v>
@@ -6803,7 +6804,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <f>'Proximal Validation (double)'!A11</f>
         <v>0.3</v>
@@ -6961,7 +6962,7 @@
         <v>0.45044866287067781</v>
       </c>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <f>'Proximal Validation (double)'!A12</f>
         <v>0.9</v>
@@ -7110,7 +7111,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <f>'Proximal Validation (double)'!A13</f>
         <v>0.1</v>
@@ -7268,7 +7269,7 @@
         <v>0.46185746069729394</v>
       </c>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <f>'Proximal Validation (double)'!A14</f>
         <v>0.9</v>
@@ -7414,7 +7415,7 @@
       </c>
       <c r="AM14" s="31"/>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <f>'Proximal Validation (double)'!A15</f>
         <v>0.9</v>
@@ -7560,7 +7561,7 @@
       </c>
       <c r="AM15" s="31"/>
     </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <f>'Proximal Validation (double)'!A16</f>
         <v>0.4</v>
@@ -7706,7 +7707,7 @@
       </c>
       <c r="AM16" s="31"/>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A17" s="10">
         <f>'Proximal Validation (double)'!A17</f>
         <v>1</v>
@@ -7852,7 +7853,7 @@
       </c>
       <c r="AM17" s="31"/>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
         <f>'Proximal Validation (double)'!A18</f>
         <v>0.4</v>
@@ -7998,7 +7999,7 @@
       </c>
       <c r="AM18" s="31"/>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <f>'Proximal Validation (double)'!A19</f>
         <v>0.1</v>
@@ -8144,7 +8145,7 @@
       </c>
       <c r="AM19" s="31"/>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <f>'Proximal Validation (double)'!A20</f>
         <v>0.9</v>
@@ -8290,7 +8291,7 @@
       </c>
       <c r="AM20" s="31"/>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <f>'Proximal Validation (double)'!A21</f>
         <v>0.1</v>
@@ -8436,7 +8437,7 @@
       </c>
       <c r="AM21" s="31"/>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <f>'Proximal Validation (double)'!A22</f>
         <v>0.1</v>
@@ -8582,7 +8583,7 @@
       </c>
       <c r="AM22" s="31"/>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <f>'Proximal Validation (double)'!A23</f>
         <v>0.9</v>
@@ -8728,7 +8729,7 @@
       </c>
       <c r="AM23" s="31"/>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <f>'Proximal Validation (double)'!A24</f>
         <v>0.2</v>
@@ -8874,7 +8875,7 @@
       </c>
       <c r="AM24" s="31"/>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <f>'Proximal Validation (double)'!A25</f>
         <v>0.6</v>
@@ -9020,7 +9021,7 @@
       </c>
       <c r="AM25" s="31"/>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <f>'Proximal Validation (double)'!A26</f>
         <v>0.7</v>
@@ -9166,7 +9167,7 @@
       </c>
       <c r="AM26" s="31"/>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <f>'Proximal Validation (double)'!A27</f>
         <v>0.1</v>
@@ -9312,7 +9313,7 @@
       </c>
       <c r="AM27" s="31"/>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <f>'Proximal Validation (double)'!A28</f>
         <v>1</v>
@@ -9458,7 +9459,7 @@
       </c>
       <c r="AM28" s="31"/>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <f>'Proximal Validation (double)'!A29</f>
         <v>0.7</v>
@@ -9604,7 +9605,7 @@
       </c>
       <c r="AM29" s="31"/>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
         <f>'Proximal Validation (double)'!A30</f>
         <v>1</v>
@@ -9750,7 +9751,7 @@
       </c>
       <c r="AM30" s="31"/>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
         <f>'Proximal Validation (double)'!A31</f>
         <v>0.1</v>
@@ -9896,7 +9897,7 @@
       </c>
       <c r="AM31" s="31"/>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
         <f>'Proximal Validation (double)'!A32</f>
         <v>0.3</v>
@@ -10042,7 +10043,7 @@
       </c>
       <c r="AM32" s="31"/>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <f>'Proximal Validation (double)'!A33</f>
         <v>1</v>
@@ -10188,7 +10189,7 @@
       </c>
       <c r="AM33" s="31"/>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <f>'Proximal Validation (double)'!A34</f>
         <v>0.1</v>
@@ -10334,7 +10335,7 @@
       </c>
       <c r="AM34" s="31"/>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A35" s="10">
         <f>'Proximal Validation (double)'!A35</f>
         <v>0.9</v>
@@ -10480,7 +10481,7 @@
       </c>
       <c r="AM35" s="31"/>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <f>'Proximal Validation (double)'!A36</f>
         <v>1</v>
@@ -10626,7 +10627,7 @@
       </c>
       <c r="AM36" s="31"/>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <f>'Proximal Validation (double)'!A37</f>
         <v>0.3</v>
@@ -10772,7 +10773,7 @@
       </c>
       <c r="AM37" s="31"/>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <f>'Proximal Validation (double)'!A38</f>
         <v>0.9</v>
@@ -10918,7 +10919,7 @@
       </c>
       <c r="AM38" s="31"/>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <f>'Proximal Validation (double)'!A39</f>
         <v>0.1</v>
@@ -11064,7 +11065,7 @@
       </c>
       <c r="AM39" s="31"/>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
         <f>'Proximal Validation (double)'!A40</f>
         <v>0.8</v>
@@ -11210,7 +11211,7 @@
       </c>
       <c r="AM40" s="31"/>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A41" s="10">
         <f>'Proximal Validation (double)'!A41</f>
         <v>1</v>
@@ -11356,7 +11357,7 @@
       </c>
       <c r="AM41" s="31"/>
     </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A42" s="10">
         <f>'Proximal Validation (double)'!A42</f>
         <v>0.2</v>
@@ -11502,7 +11503,7 @@
       </c>
       <c r="AM42" s="31"/>
     </row>
-    <row r="43" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" ht="16" x14ac:dyDescent="0.4">
       <c r="A43" s="12"/>
       <c r="B43" s="16"/>
       <c r="C43" s="17"/>
@@ -11530,7 +11531,7 @@
       <c r="Y43" s="19"/>
       <c r="Z43" s="19"/>
     </row>
-    <row r="44" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" ht="16" x14ac:dyDescent="0.4">
       <c r="A44" s="12"/>
       <c r="B44" s="16"/>
       <c r="C44" s="17"/>
@@ -11558,7 +11559,7 @@
       <c r="Y44" s="19"/>
       <c r="Z44" s="19"/>
     </row>
-    <row r="45" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" ht="16" x14ac:dyDescent="0.4">
       <c r="A45" s="12"/>
       <c r="B45" s="16"/>
       <c r="C45" s="17"/>
@@ -11586,7 +11587,7 @@
       <c r="Y45" s="19"/>
       <c r="Z45" s="19"/>
     </row>
-    <row r="46" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" ht="16" x14ac:dyDescent="0.4">
       <c r="A46" s="12"/>
       <c r="B46" s="16"/>
       <c r="C46" s="17"/>
@@ -11614,7 +11615,7 @@
       <c r="Y46" s="19"/>
       <c r="Z46" s="19"/>
     </row>
-    <row r="47" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" ht="16" x14ac:dyDescent="0.4">
       <c r="A47" s="12"/>
       <c r="B47" s="16"/>
       <c r="C47" s="17"/>
@@ -11642,7 +11643,7 @@
       <c r="Y47" s="19"/>
       <c r="Z47" s="19"/>
     </row>
-    <row r="48" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" ht="16" x14ac:dyDescent="0.4">
       <c r="A48" s="12"/>
       <c r="B48" s="16"/>
       <c r="C48" s="17"/>
@@ -11670,7 +11671,7 @@
       <c r="Y48" s="19"/>
       <c r="Z48" s="19"/>
     </row>
-    <row r="49" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A49" s="12"/>
       <c r="B49" s="16"/>
       <c r="C49" s="17"/>
@@ -11698,7 +11699,7 @@
       <c r="Y49" s="19"/>
       <c r="Z49" s="19"/>
     </row>
-    <row r="50" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A50" s="12"/>
       <c r="B50" s="16"/>
       <c r="C50" s="17"/>
@@ -11726,7 +11727,7 @@
       <c r="Y50" s="19"/>
       <c r="Z50" s="19"/>
     </row>
-    <row r="51" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A51" s="12"/>
       <c r="B51" s="16"/>
       <c r="C51" s="17"/>
@@ -11754,7 +11755,7 @@
       <c r="Y51" s="19"/>
       <c r="Z51" s="19"/>
     </row>
-    <row r="52" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A52" s="12"/>
       <c r="B52" s="16"/>
       <c r="C52" s="17"/>
@@ -11799,41 +11800,41 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4833AEA3-43CF-4C24-A2E3-E852DCD96325}">
   <dimension ref="A1:AU21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7265625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.140625" customWidth="1"/>
-    <col min="36" max="36" width="15.28515625" customWidth="1"/>
-    <col min="37" max="39" width="16.28515625" customWidth="1"/>
+    <col min="28" max="28" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.1796875" customWidth="1"/>
+    <col min="36" max="36" width="15.26953125" customWidth="1"/>
+    <col min="37" max="39" width="16.26953125" customWidth="1"/>
     <col min="40" max="40" width="11" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:47" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="33" t="s">
         <v>11</v>
       </c>
@@ -11892,7 +11893,7 @@
       <c r="AT1" s="44"/>
       <c r="AU1" s="44"/>
     </row>
-    <row r="2" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -12019,7 +12020,7 @@
       <c r="AT2" s="42"/>
       <c r="AU2" s="42"/>
     </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <f>'Proximal Validation (double)'!A10</f>
         <v>0.9</v>
@@ -12150,7 +12151,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <f>'Proximal Validation (double)'!A11</f>
         <v>0.3</v>
@@ -12290,7 +12291,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <f>'Proximal Validation (double)'!A26</f>
         <v>0.7</v>
@@ -12418,7 +12419,7 @@
       </c>
       <c r="AM5" s="31"/>
     </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <f>'Proximal Validation (double)'!A29</f>
         <v>0.7</v>
@@ -12546,7 +12547,7 @@
       </c>
       <c r="AM6" s="31"/>
     </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <f>'Proximal Validation (double)'!A30</f>
         <v>1</v>
@@ -12674,7 +12675,7 @@
       </c>
       <c r="AM7" s="31"/>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <f>'Proximal Validation (double)'!A33</f>
         <v>1</v>
@@ -12802,7 +12803,7 @@
       </c>
       <c r="AM8" s="31"/>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <f>'Proximal Validation (double)'!A34</f>
         <v>0.1</v>
@@ -12930,7 +12931,7 @@
       </c>
       <c r="AM9" s="31"/>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <f>'Proximal Validation (double)'!A39</f>
         <v>0.1</v>
@@ -13058,7 +13059,7 @@
       </c>
       <c r="AM10" s="31"/>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <f>'Proximal Validation (double)'!A40</f>
         <v>0.8</v>
@@ -13186,7 +13187,7 @@
       </c>
       <c r="AM11" s="31"/>
     </row>
-    <row r="12" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:47" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="12"/>
       <c r="B12" s="16"/>
       <c r="C12" s="17"/>
@@ -13214,7 +13215,7 @@
       <c r="Y12" s="19"/>
       <c r="Z12" s="19"/>
     </row>
-    <row r="13" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:47" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="12"/>
       <c r="B13" s="16"/>
       <c r="C13" s="17"/>
@@ -13242,7 +13243,7 @@
       <c r="Y13" s="19"/>
       <c r="Z13" s="19"/>
     </row>
-    <row r="14" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" s="12"/>
       <c r="B14" s="16"/>
       <c r="C14" s="17"/>
@@ -13270,7 +13271,7 @@
       <c r="Y14" s="19"/>
       <c r="Z14" s="19"/>
     </row>
-    <row r="15" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:47" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="12"/>
       <c r="B15" s="16"/>
       <c r="C15" s="17"/>
@@ -13298,7 +13299,7 @@
       <c r="Y15" s="19"/>
       <c r="Z15" s="19"/>
     </row>
-    <row r="16" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47" ht="16" x14ac:dyDescent="0.4">
       <c r="A16" s="12"/>
       <c r="B16" s="16"/>
       <c r="C16" s="17"/>
@@ -13326,7 +13327,7 @@
       <c r="Y16" s="19"/>
       <c r="Z16" s="19"/>
     </row>
-    <row r="17" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="12"/>
       <c r="B17" s="16"/>
       <c r="C17" s="17"/>
@@ -13354,7 +13355,7 @@
       <c r="Y17" s="19"/>
       <c r="Z17" s="19"/>
     </row>
-    <row r="18" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A18" s="12"/>
       <c r="B18" s="16"/>
       <c r="C18" s="17"/>
@@ -13382,7 +13383,7 @@
       <c r="Y18" s="19"/>
       <c r="Z18" s="19"/>
     </row>
-    <row r="19" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="12"/>
       <c r="B19" s="16"/>
       <c r="C19" s="17"/>
@@ -13410,7 +13411,7 @@
       <c r="Y19" s="19"/>
       <c r="Z19" s="19"/>
     </row>
-    <row r="20" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A20" s="12"/>
       <c r="B20" s="16"/>
       <c r="C20" s="17"/>
@@ -13438,7 +13439,7 @@
       <c r="Y20" s="19"/>
       <c r="Z20" s="19"/>
     </row>
-    <row r="21" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="12"/>
       <c r="B21" s="16"/>
       <c r="C21" s="17"/>
@@ -13482,9 +13483,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048D6981-73D2-4F8C-88D7-D5FA77AC2EB0}">
   <dimension ref="A1:M44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="45" t="s">
         <v>21</v>
       </c>
@@ -13502,7 +13503,7 @@
       <c r="L1" s="46"/>
       <c r="M1" s="47"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
@@ -13540,7 +13541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2.9205024242401099E-2</v>
       </c>
@@ -13584,7 +13585,7 @@
         <v>2.9205024242401099E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>0.92483174800872803</v>
       </c>
@@ -13628,7 +13629,7 @@
         <v>0.92483174800872803</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>0.403866738080978</v>
       </c>
@@ -13672,7 +13673,7 @@
         <v>0.403866738080978</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0.75826400518417403</v>
       </c>
@@ -13716,7 +13717,7 @@
         <v>0.75826400518417403</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>-0.43824502825737</v>
       </c>
@@ -13760,7 +13761,7 @@
         <v>-0.43824502825737</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>0.108889028429985</v>
       </c>
@@ -13804,7 +13805,7 @@
         <v>0.108889028429985</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1.80782899260521E-2</v>
       </c>
@@ -13848,7 +13849,7 @@
         <v>1.80782899260521E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>0.51686221361160301</v>
       </c>
@@ -13892,7 +13893,7 @@
         <v>0.51686221361160301</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>-0.58056563138961803</v>
       </c>
@@ -13936,7 +13937,7 @@
         <v>-0.58056563138961803</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>0.27430844306945801</v>
       </c>
@@ -13980,7 +13981,7 @@
         <v>0.27430844306945801</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>-3.6308467388153097E-2</v>
       </c>
@@ -14024,7 +14025,7 @@
         <v>-3.6308467388153097E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>4.2876139283180202E-2</v>
       </c>
@@ -14068,7 +14069,7 @@
         <v>4.2876139283180202E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>-0.18459481000900299</v>
       </c>
@@ -14112,7 +14113,7 @@
         <v>-0.18459481000900299</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>0.24705727398395499</v>
       </c>
@@ -14156,7 +14157,7 @@
         <v>0.24705727398395499</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>0.42077422142028797</v>
       </c>
@@ -14200,7 +14201,7 @@
         <v>0.42077422142028797</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>0.23870468139648399</v>
       </c>
@@ -14244,7 +14245,7 @@
         <v>0.23870468139648399</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>-0.15806177258491499</v>
       </c>
@@ -14288,7 +14289,7 @@
         <v>-0.15806177258491499</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>0.26307040452957198</v>
       </c>
@@ -14332,7 +14333,7 @@
         <v>0.26307040452957198</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>-0.20531408488750499</v>
       </c>
@@ -14376,7 +14377,7 @@
         <v>-0.20531408488750499</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>-0.54190033674240101</v>
       </c>
@@ -14420,7 +14421,7 @@
         <v>-0.54190033674240101</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>-0.70544010400772095</v>
       </c>
@@ -14464,7 +14465,7 @@
         <v>-0.70544010400772095</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>-0.29774409532547003</v>
       </c>
@@ -14508,7 +14509,7 @@
         <v>-0.29774409532547003</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>-0.93568027019500699</v>
       </c>
@@ -14552,7 +14553,7 @@
         <v>-0.93568027019500699</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>-1.0432312488555899</v>
       </c>
@@ -14596,7 +14597,7 @@
         <v>-1.0432312488555899</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>-4.6399652957916301E-2</v>
       </c>
@@ -14640,7 +14641,7 @@
         <v>-4.6399652957916301E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>-0.73725110292434703</v>
       </c>
@@ -14684,7 +14685,7 @@
         <v>-0.73725110292434703</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>-0.30814808607101402</v>
       </c>
@@ -14728,7 +14729,7 @@
         <v>-0.30814808607101402</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>-6.8177700042724595E-2</v>
       </c>
@@ -14772,7 +14773,7 @@
         <v>-6.8177700042724595E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>-0.79531830549240101</v>
       </c>
@@ -14816,7 +14817,7 @@
         <v>-0.79531830549240101</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>0.47454249858856201</v>
       </c>
@@ -14860,7 +14861,7 @@
         <v>0.47454249858856201</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>-0.949754118919373</v>
       </c>
@@ -14904,7 +14905,7 @@
         <v>-0.949754118919373</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>-0.97470813989639304</v>
       </c>
@@ -14948,7 +14949,7 @@
         <v>-0.97470813989639304</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>-1.0263080596923799</v>
       </c>
@@ -14992,7 +14993,7 @@
         <v>-1.0263080596923799</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>-0.222265124320984</v>
       </c>
@@ -15036,7 +15037,7 @@
         <v>-0.222265124320984</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>-0.63768112659454301</v>
       </c>
@@ -15080,7 +15081,7 @@
         <v>-0.63768112659454301</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>-0.99801015853881803</v>
       </c>
@@ -15124,7 +15125,7 @@
         <v>-0.99801015853881803</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>-1.1885303258895901</v>
       </c>
@@ -15168,7 +15169,7 @@
         <v>-1.1885303258895901</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>-0.66350710391998302</v>
       </c>
@@ -15212,7 +15213,7 @@
         <v>-0.66350710391998302</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>-0.207838654518127</v>
       </c>
@@ -15256,7 +15257,7 @@
         <v>-0.207838654518127</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>-1.17376625537872</v>
       </c>
@@ -15300,7 +15301,7 @@
         <v>-1.17376625537872</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>-1.0569527745246899E-2</v>
       </c>
@@ -15344,7 +15345,7 @@
         <v>-1.0569527745246899E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>-0.96642386913299605</v>
       </c>
@@ -15398,12 +15399,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15660,17 +15660,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -15695,18 +15705,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>